--- a/reports/pdf_change_20260911.xlsx
+++ b/reports/pdf_change_20260911.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,595억   ·   현금 16억(0.3%)      당일 2026-09-11  vs  전영업일 2026-09-10      매수 3종목  /  매도 5종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,659억      당일 2026-09-11  vs  전영업일 2026-09-10      매수 3종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>53</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>3588248400</v>
+        <v>3563428500</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-43</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-308528440</v>
+        <v>-306394350</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>932659200</v>
+        <v>926208000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-23</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1834148800</v>
+        <v>-1821462000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>3223220000</v>
+        <v>3200925000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-14</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-3924536000</v>
+        <v>-3897390000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>-12</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-782073600</v>
+        <v>-776664000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>-8</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-400752000</v>
+        <v>-397980000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,531억   ·   현금 44억(1.2%)      당일 2026-09-11  vs  전영업일 2026-09-10      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,489억      당일 2026-09-11  vs  전영업일 2026-09-10      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -875,7 +875,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,613억   ·   현금 42억(1.6%)      당일 2026-09-11  vs  전영업일 2026-09-10      매수 3종목  /  매도 3종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,638억      당일 2026-09-11  vs  전영업일 2026-09-10      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -971,7 +971,7 @@
         <v>115</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1533989600</v>
+        <v>1529536800</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>-224</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1623614720</v>
+        <v>-1618901760</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>41</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1381376100</v>
+        <v>1377366300</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>-105</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1663935000</v>
+        <v>-1659105000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>10</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>2228915000</v>
+        <v>2222445000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>-63</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-2135624400</v>
+        <v>-2129425200</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,000억   ·   현금 5억(0.2%)      당일 2026-09-11  vs  전영업일 2026-09-10      매수 2종목  /  매도 2종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,974억      당일 2026-09-11  vs  전영업일 2026-09-10      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1273,7 +1273,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 280억   ·   현금 1억(0.3%)      당일 2026-09-11  vs  전영업일 2026-09-10      매수 2종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 282억      당일 2026-09-11  vs  전영업일 2026-09-10      매수 2종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1369,11 +1369,11 @@
         <v>39</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>185913000</v>
+        <v>186186000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>0.33%→0.99%</t>
+          <t>0.32%→0.98%</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -1390,11 +1390,11 @@
         <v>-15</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-47197500</v>
+        <v>-51345000</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>3.80%→3.62%</t>
+          <t>4.09%→3.91%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
@@ -1413,11 +1413,11 @@
         <v>27</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>84294000</v>
+        <v>82309500</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>1.12%→1.42%</t>
+          <t>1.09%→1.38%</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -1434,11 +1434,11 @@
         <v>-13</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-29393000</v>
+        <v>-29484000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>2.13%→2.02%</t>
+          <t>2.12%→2.01%</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
@@ -1462,11 +1462,11 @@
         <v>-7</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-58849000</v>
+        <v>-58212000</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>2.57%→2.35%</t>
+          <t>2.52%→2.31%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>1.82%→1.58%</t>
+          <t>1.81%→1.57%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
@@ -1506,7 +1506,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 500억   ·   현금 4억(0.8%)      당일 2026-09-11  vs  전영업일 2026-09-10      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 493억      당일 2026-09-11  vs  전영업일 2026-09-10      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
